--- a/myProjects/3_Taximetre/Docs/Hale_Device/Hardware_List.xlsx
+++ b/myProjects/3_Taximetre/Docs/Hale_Device/Hardware_List.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Barfas_Projects\Barfas_Projects\myProjects\3_Taximetre\Docs\Hale_Device\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D69AC42-59C2-4432-B2DD-1FAC995440E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E51DFA9E-3658-4B40-AC4B-45E8663FE458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
